--- a/secondary_logistics_summary.xlsx
+++ b/secondary_logistics_summary.xlsx
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B2" t="n">
-        <v>14318971.58876421</v>
+        <v>15283745.38600003</v>
       </c>
       <c r="C2" t="n">
-        <v>162715.5862359569</v>
+        <v>145559.4798666669</v>
       </c>
       <c r="D2" t="n">
         <v>236733.5529762713</v>

--- a/secondary_logistics_summary.xlsx
+++ b/secondary_logistics_summary.xlsx
@@ -455,13 +455,13 @@
         <v>105</v>
       </c>
       <c r="B2" t="n">
-        <v>15283745.38600003</v>
+        <v>10619044.16247612</v>
       </c>
       <c r="C2" t="n">
-        <v>145559.4798666669</v>
+        <v>101133.753928344</v>
       </c>
       <c r="D2" t="n">
-        <v>236733.5529762713</v>
+        <v>74790.65440644685</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_summary.xlsx
+++ b/secondary_logistics_summary.xlsx
@@ -455,10 +455,10 @@
         <v>105</v>
       </c>
       <c r="B2" t="n">
-        <v>10619044.16247612</v>
+        <v>28939931.62476124</v>
       </c>
       <c r="C2" t="n">
-        <v>101133.753928344</v>
+        <v>275618.3964262975</v>
       </c>
       <c r="D2" t="n">
         <v>74790.65440644685</v>

--- a/secondary_logistics_summary.xlsx
+++ b/secondary_logistics_summary.xlsx
@@ -452,16 +452,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>28939931.62476124</v>
+        <v>7092493.808367994</v>
       </c>
       <c r="C2" t="n">
-        <v>275618.3964262975</v>
+        <v>1182082.301394666</v>
       </c>
       <c r="D2" t="n">
-        <v>74790.65440644685</v>
+        <v>19808.41758112768</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_summary.xlsx
+++ b/secondary_logistics_summary.xlsx
@@ -452,16 +452,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B2" t="n">
-        <v>7092493.808367994</v>
+        <v>16825860.9</v>
       </c>
       <c r="C2" t="n">
-        <v>1182082.301394666</v>
+        <v>295190.5421052632</v>
       </c>
       <c r="D2" t="n">
-        <v>19808.41758112768</v>
+        <v>37012</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_summary.xlsx
+++ b/secondary_logistics_summary.xlsx
@@ -446,22 +446,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>total_route_distance</t>
+          <t>total_route_distance_km</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" t="n">
-        <v>16825860.9</v>
+        <v>17351504</v>
       </c>
       <c r="C2" t="n">
-        <v>295190.5421052632</v>
+        <v>309848.2857142857</v>
       </c>
       <c r="D2" t="n">
-        <v>37012</v>
+        <v>39703</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_summary.xlsx
+++ b/secondary_logistics_summary.xlsx
@@ -452,16 +452,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="B2" t="n">
-        <v>17351504</v>
+        <v>24879056.7</v>
       </c>
       <c r="C2" t="n">
-        <v>309848.2857142857</v>
+        <v>253867.9255102041</v>
       </c>
       <c r="D2" t="n">
-        <v>39703</v>
+        <v>59670</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_summary.xlsx
+++ b/secondary_logistics_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,24 +444,16 @@
           <t>average_route_cost</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>total_route_distance_km</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98</v>
+        <v>504</v>
       </c>
       <c r="B2" t="n">
-        <v>24879056.7</v>
+        <v>81874757.30000001</v>
       </c>
       <c r="C2" t="n">
-        <v>253867.9255102041</v>
-      </c>
-      <c r="D2" t="n">
-        <v>59670</v>
+        <v>162449.9152777778</v>
       </c>
     </row>
   </sheetData>
